--- a/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/02_Avaliacao_Liquida_do_Governo.xlsx
+++ b/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/02_Avaliacao_Liquida_do_Governo.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1217"/>
+  <dimension ref="A1:E1218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21131,6 +21131,23 @@
       </c>
       <c r="E1217" t="n">
         <v>0.984134238898675</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B1218" t="n">
+        <v>-6.346325855223669</v>
+      </c>
+      <c r="C1218" t="n">
+        <v>-8.550059955743659</v>
+      </c>
+      <c r="D1218" t="n">
+        <v>-4.142591754703678</v>
+      </c>
+      <c r="E1218" t="n">
+        <v>1.124374793569048</v>
       </c>
     </row>
   </sheetData>
@@ -21144,7 +21161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1217"/>
+  <dimension ref="A1:E1218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41846,6 +41863,23 @@
         <v>0.6974069653051486</v>
       </c>
     </row>
+    <row r="1218">
+      <c r="A1218" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B1218" t="n">
+        <v>-7.756421377485943</v>
+      </c>
+      <c r="C1218" t="n">
+        <v>-9.216252982512732</v>
+      </c>
+      <c r="D1218" t="n">
+        <v>-6.296589772459154</v>
+      </c>
+      <c r="E1218" t="n">
+        <v>0.7448257297285841</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
